--- a/Data_clean/MCAS/Estados_US/Edos_USA_2022/ALASKA_2022.xlsx
+++ b/Data_clean/MCAS/Estados_US/Edos_USA_2022/ALASKA_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Mexicali</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -467,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Total</t>
@@ -555,12 +595,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C14">
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -628,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>León</t>
@@ -641,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -672,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -685,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -698,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C24">
@@ -711,9 +791,14 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C25">
@@ -724,9 +809,14 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C26">
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Teuchitlán</t>
@@ -750,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Tlaquepaque</t>
@@ -763,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Valle de Guadalupe</t>
+          <t>Valle De Guadalupe</t>
         </is>
       </c>
       <c r="C29">
@@ -776,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Total</t>
@@ -807,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -820,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -851,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Total</t>
@@ -882,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -913,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -926,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Total</t>
@@ -957,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Total</t>
@@ -988,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Puerto Peñasco</t>
@@ -1001,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1032,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -1045,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1068,41 +1233,6 @@
       </c>
       <c r="D49">
         <v>1</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
